--- a/site/public/downloads/cierre_2026-09_andes_labs.xlsx
+++ b/site/public/downloads/cierre_2026-09_andes_labs.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>203535812.05</v>
+        <v>208711799.05</v>
       </c>
     </row>
     <row r="10">
@@ -611,6 +611,16 @@
       </c>
       <c r="B16" t="n">
         <v>1545</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Tipo de cambio de cierre USDC (dólar cripto vendedor)</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1612.31</v>
       </c>
     </row>
   </sheetData>
@@ -688,7 +698,7 @@
         <v>0</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>10315172.7</v>
+        <v>10887596.18</v>
       </c>
     </row>
     <row r="4">
@@ -703,7 +713,7 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>22744110.4</v>
+        <v>23373642.4</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>0</v>
@@ -793,7 +803,7 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>105067844</v>
+        <v>109614299</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>0</v>
@@ -919,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>4781167.65</v>
+        <v>177604.13</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>0</v>
@@ -933,10 +943,10 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>208316979.7</v>
+        <v>208889403.18</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>208316979.7</v>
+        <v>208889403.18</v>
       </c>
     </row>
   </sheetData>
@@ -1673,7 +1683,7 @@
         <v>60000000</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>1535</v>
+        <v>1586.98</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>60000000</v>
@@ -3282,7 +3292,7 @@
         <v>1530</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>63092885.4</v>
+        <v>64954744.08</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -7768,10 +7778,10 @@
         <v>4600</v>
       </c>
       <c r="G93" s="2" t="n">
-        <v>1530</v>
+        <v>1594.25</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>7038000</v>
+        <v>7333550</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -9086,7 +9096,7 @@
         <v>45000000</v>
       </c>
       <c r="G111" s="2" t="n">
-        <v>1530</v>
+        <v>1593.47</v>
       </c>
       <c r="H111" s="2" t="n">
         <v>45000000</v>
@@ -9897,10 +9907,10 @@
         <v>5450</v>
       </c>
       <c r="G122" s="2" t="n">
-        <v>1530</v>
+        <v>1593.47</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>8338500</v>
+        <v>8684411.5</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
@@ -9970,10 +9980,10 @@
         <v>4200</v>
       </c>
       <c r="G123" s="2" t="n">
-        <v>1530</v>
+        <v>1593.47</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>6426000</v>
+        <v>6692574</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -14479,10 +14489,10 @@
         <v>5050</v>
       </c>
       <c r="G184" s="2" t="n">
-        <v>1535</v>
+        <v>1594.83</v>
       </c>
       <c r="H184" s="2" t="n">
-        <v>7751750</v>
+        <v>8053891.5</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -17784,7 +17794,7 @@
         <v>70000000</v>
       </c>
       <c r="G229" s="2" t="n">
-        <v>1545</v>
+        <v>1616.06</v>
       </c>
       <c r="H229" s="2" t="n">
         <v>70000000</v>
@@ -18003,10 +18013,10 @@
         <v>3600</v>
       </c>
       <c r="G232" s="2" t="n">
-        <v>1545</v>
+        <v>1616.06</v>
       </c>
       <c r="H232" s="2" t="n">
-        <v>5562000</v>
+        <v>5817816</v>
       </c>
       <c r="I232" t="inlineStr">
         <is>
@@ -18076,10 +18086,10 @@
         <v>3300</v>
       </c>
       <c r="G233" s="2" t="n">
-        <v>1545</v>
+        <v>1616.06</v>
       </c>
       <c r="H233" s="2" t="n">
-        <v>5098500</v>
+        <v>5332998</v>
       </c>
       <c r="I233" t="inlineStr">
         <is>
@@ -18149,10 +18159,10 @@
         <v>2900</v>
       </c>
       <c r="G234" s="2" t="n">
-        <v>1545</v>
+        <v>1616.06</v>
       </c>
       <c r="H234" s="2" t="n">
-        <v>4480500</v>
+        <v>4686574</v>
       </c>
       <c r="I234" t="inlineStr">
         <is>
@@ -18222,10 +18232,10 @@
         <v>2800</v>
       </c>
       <c r="G235" s="2" t="n">
-        <v>1545</v>
+        <v>1616.06</v>
       </c>
       <c r="H235" s="2" t="n">
-        <v>4326000</v>
+        <v>4524968</v>
       </c>
       <c r="I235" t="inlineStr">
         <is>
@@ -18295,10 +18305,10 @@
         <v>3000</v>
       </c>
       <c r="G236" s="2" t="n">
-        <v>1545</v>
+        <v>1616.06</v>
       </c>
       <c r="H236" s="2" t="n">
-        <v>4635000</v>
+        <v>4848180</v>
       </c>
       <c r="I236" t="inlineStr">
         <is>
@@ -18368,10 +18378,10 @@
         <v>4700</v>
       </c>
       <c r="G237" s="2" t="n">
-        <v>1545</v>
+        <v>1616.06</v>
       </c>
       <c r="H237" s="2" t="n">
-        <v>7261500</v>
+        <v>7595482</v>
       </c>
       <c r="I237" t="inlineStr">
         <is>
@@ -18441,10 +18451,10 @@
         <v>5200</v>
       </c>
       <c r="G238" s="2" t="n">
-        <v>1545</v>
+        <v>1616.06</v>
       </c>
       <c r="H238" s="2" t="n">
-        <v>8034000</v>
+        <v>8403512</v>
       </c>
       <c r="I238" t="inlineStr">
         <is>
@@ -18514,10 +18524,10 @@
         <v>4450</v>
       </c>
       <c r="G239" s="2" t="n">
-        <v>1545</v>
+        <v>1616.06</v>
       </c>
       <c r="H239" s="2" t="n">
-        <v>6875250</v>
+        <v>7191467</v>
       </c>
       <c r="I239" t="inlineStr">
         <is>
@@ -19029,10 +19039,10 @@
         <v>2700</v>
       </c>
       <c r="G246" s="2" t="n">
-        <v>1545</v>
+        <v>1612.31</v>
       </c>
       <c r="H246" s="2" t="n">
-        <v>4171500</v>
+        <v>4353237</v>
       </c>
       <c r="I246" t="inlineStr">
         <is>
@@ -19102,10 +19112,10 @@
         <v>4100</v>
       </c>
       <c r="G247" s="2" t="n">
-        <v>1545</v>
+        <v>1612.31</v>
       </c>
       <c r="H247" s="2" t="n">
-        <v>6334500</v>
+        <v>6610471</v>
       </c>
       <c r="I247" t="inlineStr">
         <is>
@@ -19175,10 +19185,10 @@
         <v>2500</v>
       </c>
       <c r="G248" s="2" t="n">
-        <v>1545</v>
+        <v>1612.31</v>
       </c>
       <c r="H248" s="2" t="n">
-        <v>3862500</v>
+        <v>4030775</v>
       </c>
       <c r="I248" t="inlineStr">
         <is>
@@ -19248,10 +19258,10 @@
         <v>3900</v>
       </c>
       <c r="G249" s="2" t="n">
-        <v>1545</v>
+        <v>1612.31</v>
       </c>
       <c r="H249" s="2" t="n">
-        <v>6025500</v>
+        <v>6288009</v>
       </c>
       <c r="I249" t="inlineStr">
         <is>
@@ -19321,10 +19331,10 @@
         <v>4650</v>
       </c>
       <c r="G250" s="2" t="n">
-        <v>1545</v>
+        <v>1612.31</v>
       </c>
       <c r="H250" s="2" t="n">
-        <v>7184250</v>
+        <v>7497241.5</v>
       </c>
       <c r="I250" t="inlineStr">
         <is>
@@ -19394,10 +19404,10 @@
         <v>3400</v>
       </c>
       <c r="G251" s="2" t="n">
-        <v>1545</v>
+        <v>1612.31</v>
       </c>
       <c r="H251" s="2" t="n">
-        <v>5253000</v>
+        <v>5481854</v>
       </c>
       <c r="I251" t="inlineStr">
         <is>
@@ -19467,10 +19477,10 @@
         <v>2700</v>
       </c>
       <c r="G252" s="2" t="n">
-        <v>1545</v>
+        <v>1612.31</v>
       </c>
       <c r="H252" s="2" t="n">
-        <v>4171500</v>
+        <v>4353237</v>
       </c>
       <c r="I252" t="inlineStr">
         <is>
@@ -19540,10 +19550,10 @@
         <v>3350</v>
       </c>
       <c r="G253" s="2" t="n">
-        <v>1545</v>
+        <v>1612.31</v>
       </c>
       <c r="H253" s="2" t="n">
-        <v>5175750</v>
+        <v>5401238.5</v>
       </c>
       <c r="I253" t="inlineStr">
         <is>
@@ -21161,7 +21171,7 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Official seller rate (venta) on the posting date of each movement. To validate with an accountant: buyer rate for assets, transaction date versus posting date, and Banco Nación versus BCRA Comunicación A 3500.</t>
+          <t>Seller rate (venta) on the posting date of each movement: official for dollar card spend, crypto dollar for USDC. To validate with an accountant: buyer rate for assets, transaction date versus posting date, and Banco Nación versus BCRA Comunicación A 3500.</t>
         </is>
       </c>
     </row>
@@ -21195,7 +21205,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>One USDC is treated as one US dollar at the official rate. Whether USDC should be valued at the official, MEP or crypto rate is an open question for the accountant.</t>
+          <t>USDC is valued at the crypto dollar seller rate of each day (https://api.argentinadatos.com/v1/cotizaciones/dolares/cripto), the rate at which it can be turned into pesos. One USDC is treated as one crypto dollar. Dollar card spend stays at the official rate. Whether USDC should be valued at the crypto, MEP or official rate is a question for the accountant.</t>
         </is>
       </c>
     </row>
@@ -21212,7 +21222,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>USDC received is computed from the ARS sent at the crypto dollar seller rate of that day (https://api.argentinadatos.com/v1/cotizaciones/dolares/cripto). The gap against the official rate goes to Diferencias de cambio.</t>
+          <t>USDC received is computed from the ARS sent at the crypto dollar seller rate of that day and booked at the same rate. Only the rounding the exchange keeps goes to Diferencias de cambio.</t>
         </is>
       </c>
     </row>
@@ -21229,7 +21239,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Cuenta USDC and Tarjeta corporativa a pagar are remeasured at the official seller rate of the last day of the month. The difference goes to Diferencias de cambio.</t>
+          <t>Cuenta USDC is remeasured at the crypto dollar seller rate of the last day of the month and Tarjeta corporativa a pagar at the official seller rate of that day. Paying the card with USDC moves the gap between the two rates to Diferencias de cambio, and so does each remeasurement.</t>
         </is>
       </c>
     </row>
@@ -21246,7 +21256,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Synthetic opening balances as of 2026-08-31, valued at that day's official seller rate.</t>
+          <t>Synthetic opening balances as of 2026-08-31, valued at that day's crypto seller rate for USDC and official seller rate for the card payable.</t>
         </is>
       </c>
     </row>
